--- a/data/trans_camb/P1805_2016_2023-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P1805_2016_2023-Edad-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2,52</t>
+          <t>2,55</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3,7</t>
+          <t>3,46</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,03</t>
+          <t>2,98</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 7,58</t>
+          <t>-0,43; 7,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 8,53</t>
+          <t>0,21; 7,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 6,33</t>
+          <t>0,6; 5,66</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>127,86%</t>
+          <t>129,21%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>178,78%</t>
+          <t>167,22%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>150,27%</t>
+          <t>147,39%</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-42,49; 659,59</t>
+          <t>-32,47; 584,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 791,22</t>
+          <t>-7,57; 773,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,0; 455,09</t>
+          <t>17,43; 398,88</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,28</t>
+          <t>1,44</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,47</t>
+          <t>1,83</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,44</t>
+          <t>1,66</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 4,02</t>
+          <t>-0,29; 4,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 4,22</t>
+          <t>-0,5; 4,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,11; 3,22</t>
+          <t>0,23; 3,33</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>101,18%</t>
+          <t>113,29%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>98,6%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-34,16; 626,83</t>
+          <t>-28,46; 607,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-27,65; 315,79</t>
+          <t>-24,93; 287,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 256,18</t>
+          <t>5,95; 278,93</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,76</t>
+          <t>1,35</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,35</t>
+          <t>1,17</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,56</t>
+          <t>1,26</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 4,27</t>
+          <t>-0,54; 4,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 3,35</t>
+          <t>-0,91; 3,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 3,1</t>
+          <t>-0,08; 2,68</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>51,84%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>43,39%</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-17,14; 239,36</t>
+          <t>-18,54; 240,77</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-18,1; 156,49</t>
+          <t>-21,0; 132,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 129,26</t>
+          <t>-2,9; 115,16</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>1,99</t>
+          <t>3,35</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,12</t>
+          <t>0,35</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,03</t>
+          <t>1,84</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 4,42</t>
+          <t>1,34; 5,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 2,27</t>
+          <t>-2,1; 2,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 2,69</t>
+          <t>0,57; 3,33</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>105,03%</t>
+          <t>176,57%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>60,26%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-25,07; 326,9</t>
+          <t>36,7; 508,57</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-36,64; 77,61</t>
+          <t>-36,51; 72,33</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-26,14; 108,08</t>
+          <t>14,09; 139,6</t>
         </is>
       </c>
     </row>
@@ -932,17 +932,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1,43</t>
+          <t>1,19</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-0,2</t>
+          <t>-0,43</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>0,34</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 3,31</t>
+          <t>-0,66; 2,99</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 2,25</t>
+          <t>-3,04; 2,02</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 2,21</t>
+          <t>-1,44; 1,8</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-3,63%</t>
+          <t>-7,89%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-18,43; 428,96</t>
+          <t>-28,42; 379,81</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-38,99; 58,11</t>
+          <t>-41,71; 54,55</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-21,18; 82,41</t>
+          <t>-29,32; 65,24</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>-0,16</t>
+          <t>-0,24</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>-2,18</t>
+          <t>-1,12</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-1,12</t>
+          <t>-0,74</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 0,86</t>
+          <t>-1,75; 0,93</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 0,09</t>
+          <t>-4,12; 1,31</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 0,28</t>
+          <t>-2,39; 0,59</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>-14,51%</t>
+          <t>-21,87%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>-49,96%</t>
+          <t>-25,68%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-39,43%</t>
+          <t>-25,95%</t>
         </is>
       </c>
     </row>
@@ -1097,17 +1097,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-88,74; 225,12</t>
+          <t>-80,96; 314,03</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-84,03; 4,35</t>
+          <t>-62,61; 51,91</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-73,32; 17,46</t>
+          <t>-60,21; 35,19</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>-0,37</t>
+          <t>-0,38</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>-2,13</t>
+          <t>-2,14</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-1,45</t>
+          <t>-1,46</t>
         </is>
       </c>
     </row>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 1,08</t>
+          <t>-2,45; 1,03</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 0,03</t>
+          <t>-5,18; 0,11</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 0,11</t>
+          <t>-3,25; 0,19</t>
         </is>
       </c>
     </row>
@@ -1170,17 +1170,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>-25,54%</t>
+          <t>-25,96%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>-46,05%</t>
+          <t>-46,25%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-42,96%</t>
+          <t>-43,26%</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-88,56; 324,41</t>
+          <t>-90,28; 220,17</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-73,87; 6,3</t>
+          <t>-74,06; 9,2</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-69,51; 7,74</t>
+          <t>-70,1; 14,59</t>
         </is>
       </c>
     </row>
@@ -1220,17 +1220,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>1,41</t>
+          <t>1,52</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>0,52</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>1,01</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1243,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,43</t>
+          <t>0,7; 2,4</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 1,27</t>
+          <t>-0,38; 1,41</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,6</t>
+          <t>0,42; 1,69</t>
         </is>
       </c>
     </row>
@@ -1266,17 +1266,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>36,45%</t>
         </is>
       </c>
     </row>
@@ -1289,17 +1289,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>24,69; 159,33</t>
+          <t>33,6; 157,67</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-19,8; 38,12</t>
+          <t>-9,56; 44,06</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>5,41; 65,19</t>
+          <t>13,41; 69,32</t>
         </is>
       </c>
     </row>
